--- a/C#WinForms/KursWork/SingleThread/bin/Debug/Save.xlsx
+++ b/C#WinForms/KursWork/SingleThread/bin/Debug/Save.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\C#WinForms\KursWork\SingleThread\bin\Debug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fourth\C#WinForms\KursWork\SingleThread\bin\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -424,12 +424,12 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:shape val="cone"/>
-        <c:axId val="317814840"/>
-        <c:axId val="317816408"/>
-        <c:axId val="315914272"/>
+        <c:axId val="314577160"/>
+        <c:axId val="253091712"/>
+        <c:axId val="311498672"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="317814840"/>
+        <c:axId val="314577160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -438,7 +438,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="317816408"/>
+        <c:crossAx val="253091712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -446,7 +446,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="317816408"/>
+        <c:axId val="253091712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -457,12 +457,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="317814840"/>
+        <c:crossAx val="314577160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:serAx>
-        <c:axId val="315914272"/>
+        <c:axId val="311498672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -471,7 +471,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="317816408"/>
+        <c:crossAx val="253091712"/>
         <c:crosses val="autoZero"/>
       </c:serAx>
     </c:plotArea>
